--- a/outputs/409-45.xlsx
+++ b/outputs/409-45.xlsx
@@ -60,9 +60,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -151,44 +152,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -381,7 +390,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -447,113 +456,169 @@
       <c r="E4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>44229</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="8" t="n">
         <v>44230</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="8" t="n">
         <v>44258</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="10" t="n">
         <v>44259</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -626,11 +691,11 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -650,41 +715,41 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="8" t="n">
         <v>44229</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="8" t="n">
         <v>44230</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
+      <c r="A8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -704,39 +769,39 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="8" t="n">
         <v>44258</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="8" t="n">
         <v>44259</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8"/>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/409-45.xlsx
+++ b/outputs/409-45.xlsx
@@ -60,10 +60,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -152,7 +151,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -177,14 +176,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -193,11 +184,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -390,7 +381,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -449,176 +440,106 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="6" t="n">
+        <v>44229</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>44230</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>44229</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
-        <v>44230</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="6" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A9" s="6" t="n">
+        <v>44259</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
-        <v>44259</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -691,11 +612,11 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -715,41 +636,41 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="6" t="n">
         <v>44229</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="6" t="n">
         <v>44230</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
+      <c r="A8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -769,39 +690,39 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="6" t="n">
         <v>44258</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="6" t="n">
         <v>44259</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6"/>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
